--- a/tests/testdata/excel/ファイル名/ＺＥＮＫＡＫＵ全角英字.xlsx
+++ b/tests/testdata/excel/ファイル名/ＺＥＮＫＡＫＵ全角英字.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E926BD2D-DE4E-4D5D-BBFD-F26317D9DD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B528F8-5193-4D12-B7D4-9A3BE738E9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{6DF6AF1D-F231-433E-B3AC-BDFECF541049}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FC7D0060-7961-42FE-8D55-51A35B065232}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F43431F-3920-4A54-A5F6-A10564966965}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB9C339-3582-419F-AC91-D4CE33E7AA1F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/ＺＥＮＫＡＫＵ全角英字.xlsx
+++ b/tests/testdata/excel/ファイル名/ＺＥＮＫＡＫＵ全角英字.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B528F8-5193-4D12-B7D4-9A3BE738E9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5046CEF8-2DCC-4FA7-8F56-301C4E2660CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FC7D0060-7961-42FE-8D55-51A35B065232}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{087C97A3-6FB3-4F2D-93C9-DE5B63F78D56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB9C339-3582-419F-AC91-D4CE33E7AA1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C37D75A-D96E-4669-90F0-BECD334FF151}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
